--- a/payment_forms/010_cosmetic_subscription_box_order_form--payment_forms.xlsx
+++ b/payment_forms/010_cosmetic_subscription_box_order_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -807,8 +807,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,12 +836,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'face_cream'}</t>
+          <t>face_cream</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Face Cream'}</t>
+          <t>Face Cream</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lip_balm'}</t>
+          <t>lip_balm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Lip Balm'}</t>
+          <t>Lip Balm</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'mascara'}</t>
+          <t>mascara</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Mascara'}</t>
+          <t>Mascara</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'nail_polish'}</t>
+          <t>nail_polish</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Nail Polish'}</t>
+          <t>Nail Polish</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'submit_and_pay'}</t>
+          <t>submit_and_pay</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Submit and Pay'}</t>
+          <t>Submit and Pay</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'save_for_later'}</t>
+          <t>save_for_later</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Save for Later'}</t>
+          <t>Save for Later</t>
         </is>
       </c>
     </row>
